--- a/synthetic/output/territories/territories.xlsx
+++ b/synthetic/output/territories/territories.xlsx
@@ -413,28 +413,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>area id</t>
+          <t>territory code</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>territory</t>
+          <t>area name</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>zone</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>record status</t>
+          <t>country name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
         </is>
       </c>
     </row>
@@ -456,7 +461,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -473,12 +483,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -495,12 +510,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -517,12 +537,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -539,12 +564,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -561,12 +591,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -588,7 +623,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -605,12 +645,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -627,12 +672,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -654,7 +704,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -671,12 +726,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -693,12 +753,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -720,7 +785,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -737,12 +807,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -759,12 +834,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -786,7 +866,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -803,12 +888,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -825,12 +915,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -847,12 +942,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -874,7 +974,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>

--- a/synthetic/output/territories/territories.xlsx
+++ b/synthetic/output/territories/territories.xlsx
@@ -413,33 +413,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>territory code</t>
+          <t>area id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>area name</t>
+          <t>territory name</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>zone</t>
+          <t>region name</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>country name</t>
+          <t>country</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>record status</t>
         </is>
       </c>
     </row>
@@ -978,6 +978,816 @@
         </is>
       </c>
       <c r="E21" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>T021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Varanasi Zone 21</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>T022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Jorhat Zone 22</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>T023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Burhanpur Zone 23</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>T024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Suryapet Zone 24</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>T025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Tadipatri Zone 25</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>T026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Gangtok Zone 26</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>T027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Coimbatore Zone 27</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>T028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Ambattur Zone 28</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>T029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Vijayawada Zone 29</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>T030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Salem Zone 30</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>T031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Alwar Zone 31</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>T032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Bharatpur Zone 32</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>T033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Uluberia Zone 33</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>T034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Bhagalpur Zone 34</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>T035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Madurai Zone 35</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>T036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Deoghar Zone 36</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>T037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Ujjain Zone 37</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>T038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Nadiad Zone 38</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>T039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Proddatur Zone 39</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>T040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Anantapur Zone 40</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>T041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Berhampur Zone 41</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>T042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Satna Zone 42</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>T043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Agartala Zone 43</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>T044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Rajpur Sonarpur Zone 44</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>T045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Rajpur Sonarpur Zone 45</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>T046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Tenali Zone 46</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>T047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Asansol Zone 47</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>T048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Kolhapur Zone 48</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>T049</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Kishanganj Zone 49</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>T050</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Bhimavaram Zone 50</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
